--- a/Ex4C_GTrends_marketing.xlsx
+++ b/Ex4C_GTrends_marketing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\soniatana\Documents\DataAnalytics2026\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E52ED50-6E00-4CB2-A431-F9BEE657ED0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B9DC264-1EBB-46D5-A429-CFA5342B357F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{6CECE86B-5058-4163-8490-0AF5D55E74FA}"/>
+    <workbookView xWindow="2964" yWindow="2964" windowWidth="17280" windowHeight="9960" firstSheet="2" activeTab="3" xr2:uid="{6CECE86B-5058-4163-8490-0AF5D55E74FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Geomap" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -846,7 +846,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Ex4C_GTrends_marketing (2).xlsx]Sales region lookup!PivotTable3</c:name>
+    <c:name>[Ex4C_GTrends_marketing.xlsx]Sales region lookup!PivotTable3</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -2319,7 +2319,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6AE585DF-FD3F-4B88-8FE8-58A8E7A07273}" name="PivotTable3" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6AE585DF-FD3F-4B88-8FE8-58A8E7A07273}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A15:C26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
